--- a/artfynd/A 1904-2024 artfynd.xlsx
+++ b/artfynd/A 1904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118637625</v>
+        <v>118637622</v>
       </c>
       <c r="B2" t="n">
-        <v>94370</v>
+        <v>58105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -754,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +773,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118637622</v>
+        <v>118637625</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>94370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,36 +816,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1904-2024 artfynd.xlsx
+++ b/artfynd/A 1904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118637622</v>
+        <v>118637625</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>94370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118637625</v>
+        <v>118637622</v>
       </c>
       <c r="B3" t="n">
-        <v>94370</v>
+        <v>58105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,27 +807,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1904-2024 artfynd.xlsx
+++ b/artfynd/A 1904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118637625</v>
+        <v>118637622</v>
       </c>
       <c r="B2" t="n">
-        <v>94370</v>
+        <v>58105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -754,7 +763,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +773,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118637622</v>
+        <v>118637625</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>94377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,36 +816,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1904-2024 artfynd.xlsx
+++ b/artfynd/A 1904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118637622</v>
+        <v>118637625</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>94377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118637625</v>
+        <v>118637622</v>
       </c>
       <c r="B3" t="n">
-        <v>94377</v>
+        <v>58105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,27 +807,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
